--- a/2022/Mount4/Mount4_members_final.xlsx
+++ b/2022/Mount4/Mount4_members_final.xlsx
@@ -1706,7 +1706,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>حزب الخضر اللبناني</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>حزب الحركة اللبنانية</t>
         </is>
       </c>
     </row>
